--- a/AAII_Financials/Quarterly/MODV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MODV_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
   <si>
     <t>MODV</t>
   </si>
@@ -656,289 +656,301 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>702800</v>
+      </c>
+      <c r="E8" s="3">
         <v>686900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>699100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>662300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>653900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>647800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>628200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>574500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>575800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>493100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>474400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>453600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>398500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>320600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>649500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>367300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>384800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>393400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>731700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>367800</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>585500</v>
+      </c>
+      <c r="E9" s="3">
         <v>579200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>589300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>550300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>534000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>534600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>504200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>459300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>890300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>798500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>759100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>720700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>314500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>235500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>528800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>332700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>358400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>356300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>686400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>340500</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>117300</v>
+      </c>
+      <c r="E10" s="3">
         <v>107700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>109800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>112000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>119900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>113200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>124000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>115200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-314500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-305400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-284700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-267100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>84000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>85100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>120700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>34600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>26400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>37100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>45300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -961,8 +973,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1023,8 +1036,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1085,49 +1101,52 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E14" s="3">
         <v>-600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>180500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-2800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-3300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1900</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-2600</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1135,8 +1154,8 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1147,70 +1166,76 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E15" s="3">
         <v>26100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>25900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>25700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>26000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>25700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>24800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>23900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>20300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>12600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>11800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>9000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>7300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>9900</v>
-      </c>
-      <c r="R15" s="3">
-        <v>3800</v>
       </c>
       <c r="S15" s="3">
         <v>3800</v>
       </c>
       <c r="T15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="U15" s="3">
         <v>4100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>8800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1230,132 +1255,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>687200</v>
+      </c>
+      <c r="E17" s="3">
         <v>674900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>874900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>654200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>647300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>635300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>605100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>559600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>555600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>480100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>447000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>424800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>377600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>277300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>590700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>357200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>377300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>376400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>731500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>364400</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>15600</v>
+      </c>
+      <c r="E18" s="3">
         <v>12000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-175800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>8100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>6600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>12500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>23100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>13000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>27400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>28800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>20900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>43300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>58800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>17000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1378,132 +1410,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-18300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-17800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-17000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-16000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-15500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-15600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-15500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-15400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-14700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-17700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-18800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>10000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-23500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-3300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>23900</v>
+      </c>
+      <c r="E21" s="3">
         <v>20300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-166800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>17800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>17100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>22600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>32400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>23400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>25800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>31000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>32600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>11100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>60600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>68900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>11000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-12100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>17800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>5600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1564,132 +1603,141 @@
       <c r="V22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-5800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-192700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-7900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-8900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>5500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>19200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>20300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>53300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>59000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>7300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-16000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>13700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-3900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-9000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-4500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5100</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-1200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1750,132 +1798,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-191900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-6000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-2100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>13500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>15600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>38900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>53600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>16300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-11400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>8600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-4300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-190900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-6900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-28500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>13700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-1900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>35500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>14900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-12000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>6500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-3800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1936,8 +1993,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1962,8 +2022,8 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>-100</v>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L29" s="3">
         <v>-100</v>
@@ -1972,34 +2032,37 @@
         <v>-100</v>
       </c>
       <c r="N29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-200</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-100</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-500</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>5400</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-400</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>1000</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2060,8 +2123,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2122,132 +2188,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E32" s="3">
         <v>17800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>17000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>16000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>15500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>15600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>15500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>15400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>14700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>17700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>18800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>23500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>3300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-4300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-190900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-6900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-28500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>13600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>35300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>14700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>6100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2308,137 +2383,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-4300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-190900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-6900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-28500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>13600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>35300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>14700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>6100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2461,8 +2545,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2485,70 +2570,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E41" s="3">
         <v>8100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>6900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>12800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>14500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>72700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>88000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>194100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>133100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>126500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>290900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>299600</v>
-      </c>
-      <c r="O41" s="3">
-        <v>183300</v>
       </c>
       <c r="P41" s="3">
         <v>183300</v>
       </c>
       <c r="Q41" s="3">
+        <v>183300</v>
+      </c>
+      <c r="R41" s="3">
         <v>41800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>254400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>61400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>40600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>29800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2609,102 +2698,108 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>375100</v>
+      </c>
+      <c r="E43" s="3">
         <v>340800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>346100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>299000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>296800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>272300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>279100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>280900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>237900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>302200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>239700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>223600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>210600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>172300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>177400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>175700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>183800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>201700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>161000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3">
         <v>2300</v>
-      </c>
-      <c r="E44" s="3">
-        <v>1400</v>
       </c>
       <c r="F44" s="3">
         <v>1400</v>
       </c>
       <c r="G44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="H44" s="3">
         <v>2000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1700</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N44" s="3" t="s">
         <v>8</v>
@@ -2721,8 +2816,8 @@
       <c r="R44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S44" s="3">
-        <v>0</v>
+      <c r="S44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T44" s="3">
         <v>0</v>
@@ -2733,318 +2828,336 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27600</v>
+      </c>
+      <c r="E45" s="3">
         <v>36900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>38500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>35000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>32800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>34800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>26800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>33200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>37400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>40200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>14100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>32700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>23800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>26700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>32700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>11300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>12600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>45800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>404900</v>
+      </c>
+      <c r="E46" s="3">
         <v>387900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>392900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>348200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>346200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>381700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>395800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>509100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>409800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>470700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>557000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>537200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>426600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>379300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>245900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>462800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>256400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>254900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>236600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>240000</v>
       </c>
     </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>41500</v>
+      </c>
+      <c r="E47" s="3">
         <v>45200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>45100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>43700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>41300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>43500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>80400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>83300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>83100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>134400</v>
-      </c>
-      <c r="M47" s="3">
-        <v>141200</v>
       </c>
       <c r="N47" s="3">
         <v>141200</v>
       </c>
       <c r="O47" s="3">
+        <v>141200</v>
+      </c>
+      <c r="P47" s="3">
         <v>137500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>141300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>132000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>128100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>130900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>154500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>157900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>159500</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>125400</v>
+      </c>
+      <c r="E48" s="3">
         <v>121200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>118200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>116600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>108500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>105800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>103100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>99900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>97300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>96600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>76100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>59600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>58500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>39900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>40700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>41300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>43300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>42200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>40900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1146500</v>
+      </c>
+      <c r="E49" s="3">
         <v>1166100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1185800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1388600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1408100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1428200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1449000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1395500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1415000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1422000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>775800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>781100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>790600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>222600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>227500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>153600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>155100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>156700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>158200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>159800</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3105,8 +3218,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3167,70 +3283,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E52" s="3">
         <v>42600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>42900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>44500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>40200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>30700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>31400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>25200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>11600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>26200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>11400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>12200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3291,70 +3413,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1767300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1763100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1785000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1941500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1944300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1989800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2059600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2113000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2027400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2135200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1576200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1531800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1425900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>791600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>654300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>797100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>597400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>620500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>605800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>613400</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3377,8 +3505,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3401,84 +3530,88 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>55200</v>
+      </c>
+      <c r="E57" s="3">
         <v>41800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>56000</v>
-      </c>
-      <c r="F57" s="3">
-        <v>55000</v>
       </c>
       <c r="G57" s="3">
         <v>55000</v>
       </c>
       <c r="H57" s="3">
+        <v>55000</v>
+      </c>
+      <c r="I57" s="3">
         <v>44200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>38100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>8700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>33500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>33800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>26700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>38500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>9800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>113800</v>
+      </c>
+      <c r="E58" s="3">
         <v>83000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>126500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15000</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>8</v>
@@ -3495,26 +3628,26 @@
       <c r="L58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="s">
+      <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>162300</v>
-      </c>
-      <c r="S58" s="3">
-        <v>300</v>
       </c>
       <c r="T58" s="3">
         <v>300</v>
@@ -3523,176 +3656,185 @@
         <v>300</v>
       </c>
       <c r="V58" s="3">
+        <v>300</v>
+      </c>
+      <c r="W58" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>351400</v>
+      </c>
+      <c r="E59" s="3">
         <v>392000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>350700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>424200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>436600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>489300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>542800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>574900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>518500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>542500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>513000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>452300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>316200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>243800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>192800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>128400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>140100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>157900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>150700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>165500</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>520400</v>
+      </c>
+      <c r="E60" s="3">
         <v>516900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>533200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>494200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>491600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>533500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>553400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>612900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>527200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>576000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>529200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>486100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>324800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>270600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>201300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>329100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>150200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>165800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>160600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>171500</v>
       </c>
     </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>983800</v>
+      </c>
+      <c r="E61" s="3">
         <v>982600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>981500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>980400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>979400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>978300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>977300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>976200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>975200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>974700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>487400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>486700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>486000</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3703,78 +3845,84 @@
         <v>0</v>
       </c>
       <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
         <v>100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>106900</v>
+      </c>
+      <c r="E62" s="3">
         <v>104700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>108800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>115800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>118800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>123900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>146900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>147600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>151700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>180500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>150300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>140200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>203600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>111000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>87300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>62500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>52400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>57700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>50500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3835,8 +3983,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3897,8 +4048,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3959,70 +4113,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1611100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1604200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1623600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1590400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1589700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1635700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1677600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1736800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1654200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1731200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1166900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1113000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1014300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>381600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>288600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>391600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>202700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>223700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>211400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>221100</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4045,8 +4205,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4107,8 +4268,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4169,8 +4333,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4214,25 +4381,28 @@
         <v>0</v>
       </c>
       <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
         <v>5300</v>
-      </c>
-      <c r="R70" s="3">
-        <v>77100</v>
       </c>
       <c r="S70" s="3">
         <v>77100</v>
       </c>
       <c r="T70" s="3">
-        <v>77200</v>
+        <v>77100</v>
       </c>
       <c r="U70" s="3">
         <v>77200</v>
       </c>
       <c r="V70" s="3">
+        <v>77200</v>
+      </c>
+      <c r="W70" s="3">
         <v>77400</v>
       </c>
     </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4293,70 +4463,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-19200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-14900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>176100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>180000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>187000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>215500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>212100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>211800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>243400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>250900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>237300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>218400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>221500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>185900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>198700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>183700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>190900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>183800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>186600</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4417,8 +4593,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4479,8 +4658,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4541,70 +4723,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>156200</v>
+      </c>
+      <c r="E76" s="3">
         <v>158900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>161400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>351100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>354600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>354100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>381900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>376200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>373300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>404000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>409300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>418800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>411600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>410100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>360500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>328400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>317600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>319700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>317200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4665,137 +4853,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-4300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-190900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-6900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-28500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>13600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>35300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>14700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>6100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4818,70 +5015,74 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>26600</v>
+      </c>
+      <c r="E83" s="3">
         <v>26100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>25900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>25700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>26000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>25700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>24800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>23900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>20300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>12600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>11800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9900</v>
-      </c>
-      <c r="R83" s="3">
-        <v>3800</v>
       </c>
       <c r="S83" s="3">
         <v>3800</v>
       </c>
       <c r="T83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="U83" s="3">
         <v>4100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>8800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4942,8 +5143,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5004,8 +5208,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5066,8 +5273,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5128,8 +5338,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5190,70 +5403,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-25600</v>
+      </c>
+      <c r="E89" s="3">
         <v>53500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-108200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-2700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-56000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-5700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-20300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>71500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>12100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>34500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>134600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>61200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>140000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>147200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>38800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>20900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>17000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>23100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5276,70 +5495,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-8900</v>
+        <v>-11100</v>
       </c>
       <c r="E91" s="3">
         <v>-8900</v>
       </c>
       <c r="F91" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="G91" s="3">
         <v>-13300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5400,8 +5623,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5462,70 +5688,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-8900</v>
+        <v>-11100</v>
       </c>
       <c r="E94" s="3">
         <v>-8900</v>
       </c>
       <c r="F94" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="G94" s="3">
         <v>-13300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-86200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-657100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-18600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-552600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-80000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5548,8 +5780,9 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5610,8 +5843,11 @@
       <c r="V96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5672,8 +5908,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5734,8 +5973,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5796,70 +6038,76 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-43500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>111300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>14400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>5600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>487300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-24600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-12900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>487900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>4100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-83800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>155500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>2600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-6700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5920,66 +6168,72 @@
       <c r="V101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5800</v>
+      </c>
+      <c r="E102" s="3">
         <v>1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-57800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-15300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-106500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>61100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-164200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-8700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>116300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>141700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-16600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>192800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>20000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>7300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>22100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>38300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MODV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MODV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>MODV</t>
   </si>
@@ -656,301 +656,314 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>684500</v>
+      </c>
+      <c r="E8" s="3">
         <v>702800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>686900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>699100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>662300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>653900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>647800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>628200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>574500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>575800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>493100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>474400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>453600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>398500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>320600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>649500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>367300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>384800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>393400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>731700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>367800</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>583600</v>
+      </c>
+      <c r="E9" s="3">
         <v>585500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>579200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>589300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>550300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>534000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>534600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>504200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>459300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>890300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>798500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>759100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>720700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>314500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>235500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>528800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>332700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>358400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>356300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>686400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>340500</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>100900</v>
+      </c>
+      <c r="E10" s="3">
         <v>117300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>107700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>109800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>112000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>119900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>113200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>124000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>115200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-314500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-305400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-284700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-267100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>84000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>85100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>120700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>34600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>26400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>37100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>45300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -974,8 +987,9 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1039,8 +1053,11 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1104,52 +1121,55 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>-400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>180500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-2800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-3300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-1900</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-2600</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1157,8 +1177,8 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1169,73 +1189,79 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E15" s="3">
         <v>26600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>26100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>25900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>25700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>26000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>25700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>24800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>23900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>20300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>12600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>11800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>12200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>9000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>7300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>9900</v>
-      </c>
-      <c r="S15" s="3">
-        <v>3800</v>
       </c>
       <c r="T15" s="3">
         <v>3800</v>
       </c>
       <c r="U15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="V15" s="3">
         <v>4100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>8800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1256,138 +1282,145 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>687800</v>
+      </c>
+      <c r="E17" s="3">
         <v>687200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>674900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>874900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>654200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>647300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>635300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>605100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>559600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>555600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>480100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>447000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>424800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>377600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>277300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>590700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>357200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>377300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>376400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>731500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>364400</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-3300</v>
+      </c>
+      <c r="E18" s="3">
         <v>15600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>12000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-175800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>12500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>23100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>20200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>13000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>27400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>28800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>20900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>43300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>58800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>17000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,138 +1444,145 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-18700</v>
+      </c>
+      <c r="E20" s="3">
         <v>-18300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-17800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-17000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-16000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-15500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-15600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-15500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-15400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-14700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-17700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-8200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-18800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>10000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-23500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E21" s="3">
         <v>23900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>20300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-166800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>17800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>22600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>32400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>23400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>25800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>31000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>32600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>11100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>60600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>68900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-12100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>17800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1606,138 +1646,147 @@
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-22100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-2700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-5800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-192700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-7900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>7700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>5500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-4700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>19200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>20300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>53300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>59000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>7300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-16000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>13700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
         <v>-1700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-3900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-9000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-4500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-1200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1801,138 +1850,147 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-21500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-2700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-4100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-191900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-6000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-2100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>5400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>13500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>15600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>38900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>53600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-11400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>8600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-4300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-190900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-6900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-28500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>13700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>18800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>35500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>14900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-12000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>6500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-3800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1996,8 +2054,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2025,8 +2086,8 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>-100</v>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>-100</v>
@@ -2035,34 +2096,37 @@
         <v>-100</v>
       </c>
       <c r="O29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-200</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-100</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-500</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>5400</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-400</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>1000</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2126,8 +2190,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2191,138 +2258,147 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E32" s="3">
         <v>18300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>17800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>17000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>16000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>15500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>15600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>15500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>15400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>14700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>17700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>8200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>18800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-10000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>23500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-4300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-190900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-6900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-28500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>13600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>18800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>35300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>14700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>6100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2386,143 +2462,152 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-4300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-190900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-6900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-28500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>13600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>18800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>35300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>14700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>6100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2546,8 +2631,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2571,73 +2657,77 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10300</v>
+      </c>
+      <c r="E41" s="3">
         <v>2200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>6900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>12800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>14500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>72700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>88000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>194100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>133100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>126500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>290900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>299600</v>
-      </c>
-      <c r="P41" s="3">
-        <v>183300</v>
       </c>
       <c r="Q41" s="3">
         <v>183300</v>
       </c>
       <c r="R41" s="3">
+        <v>183300</v>
+      </c>
+      <c r="S41" s="3">
         <v>41800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>254400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>61400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>40600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>29800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2701,108 +2791,114 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>362900</v>
+      </c>
+      <c r="E43" s="3">
         <v>375100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>340800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>346100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>299000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>296800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>272300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>279100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>280900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>237900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>302200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>239700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>223600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>210600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>172300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>177400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>175700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>183800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>201700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>161000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E44" s="3">
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3">
         <v>2300</v>
-      </c>
-      <c r="F44" s="3">
-        <v>1400</v>
       </c>
       <c r="G44" s="3">
         <v>1400</v>
       </c>
       <c r="H44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I44" s="3">
         <v>2000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1700</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>8</v>
@@ -2819,8 +2915,8 @@
       <c r="S44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T44" s="3">
-        <v>0</v>
+      <c r="T44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U44" s="3">
         <v>0</v>
@@ -2831,333 +2927,351 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E45" s="3">
         <v>27600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>36900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>38500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>35000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>32800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>34800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>33200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>37400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>40200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>26400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>14100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>32700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>23800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>32700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>11300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>45800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>404000</v>
+      </c>
+      <c r="E46" s="3">
         <v>404900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>387900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>392900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>348200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>346200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>381700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>395800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>509100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>409800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>470700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>557000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>537200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>426600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>379300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>245900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>462800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>256400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>254900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>236600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>240000</v>
       </c>
     </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E47" s="3">
         <v>41500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>45200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>45100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>43700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>41300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>43500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>80400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>83300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>83100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>134400</v>
-      </c>
-      <c r="N47" s="3">
-        <v>141200</v>
       </c>
       <c r="O47" s="3">
         <v>141200</v>
       </c>
       <c r="P47" s="3">
+        <v>141200</v>
+      </c>
+      <c r="Q47" s="3">
         <v>137500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>141300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>132000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>128100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>130900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>154500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>157900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>159500</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>126800</v>
+      </c>
+      <c r="E48" s="3">
         <v>125400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>121200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>118200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>116600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>108500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>105800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>103100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>99900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>97300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>96600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>76100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>59600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>58500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>39900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>40700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>41300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>43300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>42200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>40900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1126600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1146500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1166100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1185800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1388600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1408100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1428200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1449000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1395500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1415000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1422000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>775800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>781100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>790600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>222600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>227500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>153600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>155100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>156700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>158200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>159800</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3221,8 +3335,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3286,73 +3403,79 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>46800</v>
+      </c>
+      <c r="E52" s="3">
         <v>48900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>42600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>42900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>44500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>30700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>31400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>22200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>11600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>26200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>11400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>12200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3416,73 +3539,79 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1764000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1767300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1763100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1785000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1941500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1944300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1989800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2059600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2113000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2027400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2135200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1576200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1531800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1425900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>791600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>654300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>797100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>597400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>620500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>605800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>613400</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,8 +3635,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3531,90 +3661,94 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E57" s="3">
         <v>55200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>41800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>56000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>55000</v>
       </c>
       <c r="H57" s="3">
         <v>55000</v>
       </c>
       <c r="I57" s="3">
+        <v>55000</v>
+      </c>
+      <c r="J57" s="3">
         <v>44200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>38100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>33500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>16300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>33800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>26700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>38500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>9800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>7600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>121000</v>
+      </c>
+      <c r="E58" s="3">
         <v>113800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>83000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>126500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>15000</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>8</v>
@@ -3631,26 +3765,26 @@
       <c r="M58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
+      <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>162300</v>
-      </c>
-      <c r="T58" s="3">
-        <v>300</v>
       </c>
       <c r="U58" s="3">
         <v>300</v>
@@ -3659,185 +3793,194 @@
         <v>300</v>
       </c>
       <c r="W58" s="3">
+        <v>300</v>
+      </c>
+      <c r="X58" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>363700</v>
+      </c>
+      <c r="E59" s="3">
         <v>351400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>392000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>350700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>424200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>436600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>489300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>542800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>574900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>518500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>542500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>513000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>452300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>316200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>243800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>192800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>128400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>140100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>157900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>150700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>165500</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>539300</v>
+      </c>
+      <c r="E60" s="3">
         <v>520400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>516900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>533200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>494200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>491600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>533500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>553400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>612900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>527200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>576000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>529200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>486100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>324800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>270600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>201300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>329100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>150200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>165800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>160600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>171500</v>
       </c>
     </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>984900</v>
+      </c>
+      <c r="E61" s="3">
         <v>983800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>982600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>981500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>980400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>979400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>978300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>977300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>976200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>975200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>974700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>487400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>486700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>486000</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3848,81 +3991,87 @@
         <v>0</v>
       </c>
       <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
         <v>100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>104000</v>
+      </c>
+      <c r="E62" s="3">
         <v>106900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>104700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>108800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>115800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>118800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>123900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>146900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>147600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>151700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>180500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>150300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>140200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>203600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>111000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>87300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>62500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>52400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>57700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>50500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3986,8 +4135,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4051,8 +4203,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4116,73 +4271,79 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1628200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1611100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1604200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1623600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1590400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1589700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1635700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1677600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1736800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1654200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1731200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1166900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1113000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1014300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>381600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>288600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>391600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>202700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>223700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>211400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>221100</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4206,8 +4367,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4271,8 +4433,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4336,8 +4501,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4384,25 +4552,28 @@
         <v>0</v>
       </c>
       <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
         <v>5300</v>
-      </c>
-      <c r="S70" s="3">
-        <v>77100</v>
       </c>
       <c r="T70" s="3">
         <v>77100</v>
       </c>
       <c r="U70" s="3">
-        <v>77200</v>
+        <v>77100</v>
       </c>
       <c r="V70" s="3">
         <v>77200</v>
       </c>
       <c r="W70" s="3">
+        <v>77200</v>
+      </c>
+      <c r="X70" s="3">
         <v>77400</v>
       </c>
     </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4466,73 +4637,79 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-24400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-19200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-14900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>176100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>180000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>187000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>215500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>212100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>211800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>243400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>250900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>237300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>218400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>221500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>185900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>198700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>183700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>190900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>183800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>186600</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4596,8 +4773,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4661,8 +4841,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4726,73 +4909,79 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>135800</v>
+      </c>
+      <c r="E76" s="3">
         <v>156200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>158900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>161400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>351100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>354600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>354100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>381900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>376200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>373300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>404000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>409300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>418800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>411600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>410100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>360500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>328400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>317600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>319700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>317200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4856,143 +5045,152 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-4300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-190900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-6900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-28500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>13600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>18800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>35300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>14700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>6100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5016,73 +5214,77 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E83" s="3">
         <v>26600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>26100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>25900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>25700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>26000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>25700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>24800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>11800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>9000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>9900</v>
-      </c>
-      <c r="S83" s="3">
-        <v>3800</v>
       </c>
       <c r="T83" s="3">
         <v>3800</v>
       </c>
       <c r="U83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="V83" s="3">
         <v>4100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>8800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5146,8 +5348,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5211,8 +5416,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5276,8 +5484,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5341,8 +5552,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5406,73 +5620,79 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-25600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>53500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-108200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-56000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-5700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-20300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>71500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>34500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>134600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>61200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>140000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>147200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>38800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>20900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>17000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>23100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5496,73 +5716,77 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11100</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-8900</v>
       </c>
       <c r="F91" s="3">
         <v>-8900</v>
       </c>
       <c r="G91" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="H91" s="3">
         <v>-13300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-1600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5626,8 +5850,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5691,73 +5918,79 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11100</v>
-      </c>
-      <c r="E94" s="3">
-        <v>-8900</v>
       </c>
       <c r="F94" s="3">
         <v>-8900</v>
       </c>
       <c r="G94" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="H94" s="3">
         <v>-13300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-86200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-4500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-657100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-18600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-552600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-80000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-1600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5781,8 +6014,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5846,8 +6080,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5911,8 +6148,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5976,8 +6216,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6041,73 +6284,79 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E100" s="3">
         <v>31000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-43500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>111300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>14400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>5600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>487300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-24600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-12900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>487900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>4100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-83800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>155500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-6700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6171,69 +6420,75 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-57800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-15300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-106500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>61100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-164200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-8700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>116300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>141700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-16600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>192800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>20000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>7300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>22100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>38300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MODV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MODV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
   <si>
     <t>MODV</t>
   </si>
@@ -656,314 +656,327 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>698300</v>
+      </c>
+      <c r="E8" s="3">
         <v>684500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>702800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>686900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>699100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>662300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>653900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>647800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>628200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>574500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>575800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>493100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>474400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>453600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>398500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>320600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>649500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>367300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>384800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>393400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>731700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>367800</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>588100</v>
+      </c>
+      <c r="E9" s="3">
         <v>583600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>585500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>579200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>589300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>550300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>534000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>534600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>504200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>459300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>890300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>798500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>759100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>720700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>314500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>235500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>528800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>332700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>358400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>356300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>686400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>340500</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>110200</v>
+      </c>
+      <c r="E10" s="3">
         <v>100900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>117300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>107700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>109800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>112000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>119900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>113200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>124000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>115200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-314500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-305400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-284700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-267100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>84000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>85100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>120700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>34600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>26400</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>37100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>45300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -988,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,55 +1141,58 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>105300</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>-400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>180500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-2800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-3300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-1900</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1180,8 +1200,8 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1192,76 +1212,82 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E15" s="3">
         <v>27100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>26600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>26100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>25900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>25700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>26000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>25700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>24800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>23900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>20300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>12600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>11800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>12200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>9000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>7300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>9900</v>
-      </c>
-      <c r="T15" s="3">
-        <v>3800</v>
       </c>
       <c r="U15" s="3">
         <v>3800</v>
       </c>
       <c r="V15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="W15" s="3">
         <v>4100</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>8800</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,144 +1309,151 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>797200</v>
+      </c>
+      <c r="E17" s="3">
         <v>687800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>687200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>674900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>874900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>654200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>647300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>635300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>605100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>559600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>555600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>480100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>447000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>424800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>377600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>277300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>590700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>357200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>377300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>376400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>731500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>364400</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-98900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-3300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>15600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>12000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-175800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>8100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>6600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>12500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>23100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>20200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>13000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>27400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>28800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>20900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>43300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>58800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>17000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,144 +1478,151 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-20000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-18700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-18300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-17800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-17000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-16000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-15500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-15600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-15500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-15400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-14700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-17700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-8200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-18800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>10000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-23500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-91100</v>
+      </c>
+      <c r="E21" s="3">
         <v>5000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>23900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>20300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-166800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>17800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>17100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>22600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>32400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>23400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>25800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>31000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>32600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>11100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>60600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>68900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>11000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-12100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>17800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1649,144 +1689,153 @@
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-118900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-22100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-5800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-192700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-7900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>5500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-4700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>19200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>20300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>53300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>59000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>7300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-16000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>13700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-3300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-500</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
         <v>-1700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-3900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-2000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-9000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-4500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-1200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,144 +1902,153 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-128400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-21500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-2700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-4100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-191900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-6000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-5000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-2100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>13500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>15600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>38900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>53600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>16300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-11400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>8600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-2100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-128900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-22300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-5300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-4300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-190900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-6900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-28500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-31500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>13700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-1900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>35500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>14900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-12000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>6500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-3800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2089,8 +2150,8 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>-100</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>-100</v>
@@ -2099,34 +2160,37 @@
         <v>-100</v>
       </c>
       <c r="P29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
         <v>-200</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-100</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-500</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>5400</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>1000</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,144 +2328,153 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E32" s="3">
         <v>18700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>18300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>17800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>17000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>16000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>15500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>15600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>15500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>15400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>14700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>17700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>8200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>18800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-10000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>23500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-128900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-22300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-5300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-4300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-190900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-6900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-28500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-31600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>13600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>35300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>14700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>6100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-2900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,149 +2541,158 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-128900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-22300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-5300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-4300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-190900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-6900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-28500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-31600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>13600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>35300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>14700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>6100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-2900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,76 +2744,80 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E41" s="3">
         <v>10300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>12800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>14500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>72700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>88000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>194100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>133100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>126500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>290900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>299600</v>
-      </c>
-      <c r="Q41" s="3">
-        <v>183300</v>
       </c>
       <c r="R41" s="3">
         <v>183300</v>
       </c>
       <c r="S41" s="3">
+        <v>183300</v>
+      </c>
+      <c r="T41" s="3">
         <v>41800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>254400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>61400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>40600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>29800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,76 +2884,82 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>403600</v>
+      </c>
+      <c r="E43" s="3">
         <v>362900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>375100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>340800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>346100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>299000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>296800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>272300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>279100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>280900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>237900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>302200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>239700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>223600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>210600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>172300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>177400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>175700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>183800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>201700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>161000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2873,35 +2969,35 @@
       <c r="E44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3">
         <v>2300</v>
-      </c>
-      <c r="G44" s="3">
-        <v>1400</v>
       </c>
       <c r="H44" s="3">
         <v>1400</v>
       </c>
       <c r="I44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J44" s="3">
         <v>2000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1700</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P44" s="3" t="s">
         <v>8</v>
@@ -2918,8 +3014,8 @@
       <c r="T44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U44" s="3">
-        <v>0</v>
+      <c r="U44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V44" s="3">
         <v>0</v>
@@ -2930,348 +3026,366 @@
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E45" s="3">
         <v>30800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>27600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>36900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>38500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>35000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>32800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>34800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>33200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>37400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>40200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>26400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>32700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>23800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>26700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>32700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>11300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>45800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>456700</v>
+      </c>
+      <c r="E46" s="3">
         <v>404000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>404900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>387900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>392900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>348200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>346200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>381700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>395800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>509100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>409800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>470700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>557000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>537200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>426600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>379300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>245900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>462800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>256400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>254900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>236600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>240000</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E47" s="3">
         <v>59800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>41500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>45200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>45100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>43700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>41300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>43500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>80400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>83300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>83100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>134400</v>
-      </c>
-      <c r="O47" s="3">
-        <v>141200</v>
       </c>
       <c r="P47" s="3">
         <v>141200</v>
       </c>
       <c r="Q47" s="3">
+        <v>141200</v>
+      </c>
+      <c r="R47" s="3">
         <v>137500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>141300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>132000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>128100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>130900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>154500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>157900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>159500</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>123600</v>
+      </c>
+      <c r="E48" s="3">
         <v>126800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>125400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>121200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>118200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>116600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>108500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>105800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>103100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>99900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>97300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>96600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>76100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>59600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>58500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>39900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>40700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>41300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>43300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>42200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>40900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1001600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1126600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1146500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1166100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1185800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1388600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1408100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1428200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1449000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1395500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1415000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1422000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>775800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>781100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>790600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>222600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>227500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>153600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>155100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>156700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>158200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>159800</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,76 +3523,82 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E52" s="3">
         <v>46800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>48900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>42600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>42900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>44500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>40200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>31400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>22200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>11600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>26200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>11400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>12200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,76 +3665,82 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1676100</v>
+      </c>
+      <c r="E54" s="3">
         <v>1764000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1767300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1763100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1785000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1941500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1944300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1989800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2059600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2113000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2027400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2135200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1576200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1531800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1425900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>791600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>654300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>797100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>597400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>620500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>605800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>613400</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,96 +3792,100 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E57" s="3">
         <v>54600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>55200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>41800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>56000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>55000</v>
       </c>
       <c r="I57" s="3">
         <v>55000</v>
       </c>
       <c r="J57" s="3">
+        <v>55000</v>
+      </c>
+      <c r="K57" s="3">
         <v>44200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>38100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>33500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>16300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>33800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>26700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>38500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>9800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>7600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>183000</v>
+      </c>
+      <c r="E58" s="3">
         <v>121000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>113800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>83000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>126500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>15000</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>8</v>
@@ -3768,26 +3902,26 @@
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3" t="s">
+      <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>162300</v>
-      </c>
-      <c r="U58" s="3">
-        <v>300</v>
       </c>
       <c r="V58" s="3">
         <v>300</v>
@@ -3796,194 +3930,203 @@
         <v>300</v>
       </c>
       <c r="X58" s="3">
+        <v>300</v>
+      </c>
+      <c r="Y58" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>323600</v>
+      </c>
+      <c r="E59" s="3">
         <v>363700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>351400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>392000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>350700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>424200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>436600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>489300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>542800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>574900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>518500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>542500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>513000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>452300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>316200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>243800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>192800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>128400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>140100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>157900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>150700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>165500</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>568600</v>
+      </c>
+      <c r="E60" s="3">
         <v>539300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>520400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>516900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>533200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>494200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>491600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>533500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>553400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>612900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>527200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>576000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>529200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>486100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>324800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>270600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>201300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>329100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>150200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>165800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>160600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>171500</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>986100</v>
+      </c>
+      <c r="E61" s="3">
         <v>984900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>983800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>982600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>981500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>980400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>979400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>978300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>977300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>976200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>975200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>974700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>487400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>486700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>486000</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3994,84 +4137,90 @@
         <v>0</v>
       </c>
       <c r="V61" s="3">
+        <v>0</v>
+      </c>
+      <c r="W61" s="3">
         <v>100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>112000</v>
+      </c>
+      <c r="E62" s="3">
         <v>104000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>106900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>104700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>108800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>115800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>118800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>123900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>146900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>147600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>151700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>180500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>150300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>140200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>203600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>111000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>87300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>62500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>52400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>57700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>50500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,76 +4429,82 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1666600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1628200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1611100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1604200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1623600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1590400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1589700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1635700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1677600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1736800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1654200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1731200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1166900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1113000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1014300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>381600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>288600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>391600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>202700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>223700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>211400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>221100</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4555,25 +4723,28 @@
         <v>0</v>
       </c>
       <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
         <v>5300</v>
-      </c>
-      <c r="T70" s="3">
-        <v>77100</v>
       </c>
       <c r="U70" s="3">
         <v>77100</v>
       </c>
       <c r="V70" s="3">
-        <v>77200</v>
+        <v>77100</v>
       </c>
       <c r="W70" s="3">
         <v>77200</v>
       </c>
       <c r="X70" s="3">
+        <v>77200</v>
+      </c>
+      <c r="Y70" s="3">
         <v>77400</v>
       </c>
     </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,76 +4811,82 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-175600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-46700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-24400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-19200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-14900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>176100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>180000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>187000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>215500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>212100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>211800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>243400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>250900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>237300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>218400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>221500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>185900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>198700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>183700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>190900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>183800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>186600</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,76 +5095,82 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>9500</v>
+      </c>
+      <c r="E76" s="3">
         <v>135800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>156200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>158900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>161400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>351100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>354600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>354100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>381900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>376200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>373300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>404000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>409300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>418800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>411600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>410100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>360500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>328400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>317600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>319700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>317200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,149 +5237,158 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-128900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-22300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-5300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-4300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-190900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-6900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-28500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-31600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>13600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>35300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>14700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>6100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-2900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,76 +5413,80 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E83" s="3">
         <v>27100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>26600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>26100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>25900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>25700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>26000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>25700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>24800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>20300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>9900</v>
-      </c>
-      <c r="T83" s="3">
-        <v>3800</v>
       </c>
       <c r="U83" s="3">
         <v>3800</v>
       </c>
       <c r="V83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="W83" s="3">
         <v>4100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>8800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,76 +5837,82 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-55300</v>
+      </c>
+      <c r="E89" s="3">
         <v>9600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-25600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>53500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-108200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-56000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-5700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-20300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>71500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>34500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>134600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>61200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>140000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>147200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>38800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>20900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>17000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>23100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,76 +5937,80 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11100</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-8900</v>
       </c>
       <c r="G91" s="3">
         <v>-8900</v>
       </c>
       <c r="H91" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="I91" s="3">
         <v>-13300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-1600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,76 +6148,82 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11100</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-8900</v>
       </c>
       <c r="G94" s="3">
         <v>-8900</v>
       </c>
       <c r="H94" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="I94" s="3">
         <v>-13300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-86200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-657100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-18600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-552600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-80000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-3600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,76 +6530,82 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>62200</v>
+      </c>
+      <c r="E100" s="3">
         <v>6400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>31000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-43500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>111300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>14400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>5600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>487300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-24600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-12900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>487900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>4100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-83800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>155500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-6700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6423,72 +6672,78 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>200</v>
+      </c>
+      <c r="E102" s="3">
         <v>8100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-57800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-15300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-106500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>61100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-164200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-8700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>116300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>141700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-16600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>192800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>20000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>7300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>22100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>38300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MODV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MODV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>MODV</t>
   </si>
@@ -656,327 +656,340 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>702000</v>
+      </c>
+      <c r="E8" s="3">
         <v>698300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>684500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>702800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>686900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>699100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>662300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>653900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>647800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>628200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>574500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>575800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>493100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>474400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>453600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>398500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>320600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>649500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>367300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>384800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>393400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>731700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>367800</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>597900</v>
+      </c>
+      <c r="E9" s="3">
         <v>588100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>583600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>585500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>579200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>589300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>550300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>534000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>534600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>504200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>459300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>890300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>798500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>759100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>720700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>314500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>235500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>528800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>332700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>358400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>356300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>686400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>340500</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>104100</v>
+      </c>
+      <c r="E10" s="3">
         <v>110200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>100900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>117300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>107700</v>
       </c>
-      <c r="H10" s="3">
-        <v>109800</v>
-      </c>
       <c r="I10" s="3">
+        <v>109900</v>
+      </c>
+      <c r="J10" s="3">
         <v>112000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>119900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>113200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>124000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>115200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-314500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-305400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-284700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-267100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>84000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>85100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>120700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>34600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>26400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>37100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>45300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1002,8 +1015,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1073,8 +1087,11 @@
       <c r="Y12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1144,58 +1161,61 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E14" s="3">
         <v>105300</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>-400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>180500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-2800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-3300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-1900</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-2600</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1203,8 +1223,8 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1215,79 +1235,85 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E15" s="3">
         <v>27800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>27100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>26600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>26100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>25900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>25700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>26000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>25700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>24800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>23900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>20300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>12600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>11800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>12200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>9000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>7300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>9900</v>
-      </c>
-      <c r="U15" s="3">
-        <v>3800</v>
       </c>
       <c r="V15" s="3">
         <v>3800</v>
       </c>
       <c r="W15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="X15" s="3">
         <v>4100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>8800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1310,150 +1336,157 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>797200</v>
+        <v>696800</v>
       </c>
       <c r="E17" s="3">
+        <v>691900</v>
+      </c>
+      <c r="F17" s="3">
         <v>687800</v>
       </c>
-      <c r="F17" s="3">
-        <v>687200</v>
-      </c>
       <c r="G17" s="3">
-        <v>674900</v>
+        <v>687500</v>
       </c>
       <c r="H17" s="3">
-        <v>874900</v>
+        <v>675400</v>
       </c>
       <c r="I17" s="3">
-        <v>654200</v>
+        <v>694400</v>
       </c>
       <c r="J17" s="3">
+        <v>655700</v>
+      </c>
+      <c r="K17" s="3">
         <v>647300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>635300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>605100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>559600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>555600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>480100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>447000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>424800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>377600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>277300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>590700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>357200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>377300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>376400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>731500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>364400</v>
       </c>
     </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-98900</v>
+        <v>5300</v>
       </c>
       <c r="E18" s="3">
-        <v>-3300</v>
+        <v>6400</v>
       </c>
       <c r="F18" s="3">
-        <v>15600</v>
+        <v>-3400</v>
       </c>
       <c r="G18" s="3">
-        <v>12000</v>
+        <v>15300</v>
       </c>
       <c r="H18" s="3">
-        <v>-175800</v>
+        <v>11500</v>
       </c>
       <c r="I18" s="3">
-        <v>8100</v>
+        <v>4700</v>
       </c>
       <c r="J18" s="3">
         <v>6600</v>
       </c>
       <c r="K18" s="3">
+        <v>6600</v>
+      </c>
+      <c r="L18" s="3">
         <v>12500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>23100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>20200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>13000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>27400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>28800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>20900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>43300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>58800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>17000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1479,173 +1512,180 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-20000</v>
+        <v>2600</v>
       </c>
       <c r="E20" s="3">
-        <v>-18700</v>
+        <v>500</v>
       </c>
       <c r="F20" s="3">
-        <v>-18300</v>
+        <v>800</v>
       </c>
       <c r="G20" s="3">
-        <v>-17800</v>
+        <v>2500</v>
       </c>
       <c r="H20" s="3">
-        <v>-17000</v>
+        <v>200</v>
       </c>
       <c r="I20" s="3">
-        <v>-16000</v>
+        <v>-1000</v>
       </c>
       <c r="J20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="K20" s="3">
         <v>-15500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-15600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-15500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-15400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-14700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-17700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-8200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-18800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>10000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-23500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-91100</v>
+        <v>30600</v>
       </c>
       <c r="E21" s="3">
-        <v>5000</v>
+        <v>33700</v>
       </c>
       <c r="F21" s="3">
-        <v>23900</v>
+        <v>22900</v>
       </c>
       <c r="G21" s="3">
-        <v>20300</v>
+        <v>39300</v>
       </c>
       <c r="H21" s="3">
-        <v>-166800</v>
+        <v>37400</v>
       </c>
       <c r="I21" s="3">
+        <v>31600</v>
+      </c>
+      <c r="J21" s="3">
+        <v>34400</v>
+      </c>
+      <c r="K21" s="3">
+        <v>17100</v>
+      </c>
+      <c r="L21" s="3">
+        <v>22600</v>
+      </c>
+      <c r="M21" s="3">
+        <v>32400</v>
+      </c>
+      <c r="N21" s="3">
+        <v>23400</v>
+      </c>
+      <c r="O21" s="3">
+        <v>25800</v>
+      </c>
+      <c r="P21" s="3">
+        <v>7900</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>31000</v>
+      </c>
+      <c r="R21" s="3">
+        <v>32600</v>
+      </c>
+      <c r="S21" s="3">
+        <v>11100</v>
+      </c>
+      <c r="T21" s="3">
+        <v>60600</v>
+      </c>
+      <c r="U21" s="3">
+        <v>68900</v>
+      </c>
+      <c r="V21" s="3">
+        <v>11000</v>
+      </c>
+      <c r="W21" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="X21" s="3">
         <v>17800</v>
       </c>
-      <c r="J21" s="3">
-        <v>17100</v>
-      </c>
-      <c r="K21" s="3">
-        <v>22600</v>
-      </c>
-      <c r="L21" s="3">
-        <v>32400</v>
-      </c>
-      <c r="M21" s="3">
-        <v>23400</v>
-      </c>
-      <c r="N21" s="3">
-        <v>25800</v>
-      </c>
-      <c r="O21" s="3">
-        <v>7900</v>
-      </c>
-      <c r="P21" s="3">
-        <v>31000</v>
-      </c>
-      <c r="Q21" s="3">
-        <v>32600</v>
-      </c>
-      <c r="R21" s="3">
-        <v>11100</v>
-      </c>
-      <c r="S21" s="3">
-        <v>60600</v>
-      </c>
-      <c r="T21" s="3">
-        <v>68900</v>
-      </c>
-      <c r="U21" s="3">
-        <v>11000</v>
-      </c>
-      <c r="V21" s="3">
-        <v>-12100</v>
-      </c>
-      <c r="W21" s="3">
-        <v>17800</v>
-      </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>5600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>28500</v>
       </c>
       <c r="E22" s="3">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F22" s="3">
-        <v>0</v>
+        <v>18700</v>
       </c>
       <c r="G22" s="3">
-        <v>0</v>
+        <v>18400</v>
       </c>
       <c r="H22" s="3">
-        <v>0</v>
+        <v>17800</v>
       </c>
       <c r="I22" s="3">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="J22" s="3">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1692,150 +1732,159 @@
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-118900</v>
+        <v>-37700</v>
       </c>
       <c r="E23" s="3">
-        <v>-22100</v>
+        <v>-119300</v>
       </c>
       <c r="F23" s="3">
-        <v>-2700</v>
+        <v>-22800</v>
       </c>
       <c r="G23" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="H23" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="I23" s="3">
+        <v>-191800</v>
+      </c>
+      <c r="J23" s="3">
         <v>-5800</v>
       </c>
-      <c r="H23" s="3">
-        <v>-192700</v>
-      </c>
-      <c r="I23" s="3">
-        <v>-7900</v>
-      </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>5500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-4700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>19200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>20300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>53300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>59000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>7300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-16000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>13700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E24" s="3">
         <v>9600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-500</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>-1700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-3900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-2000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>14400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-9000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-4500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1905,150 +1954,159 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-128400</v>
+        <v>-26600</v>
       </c>
       <c r="E26" s="3">
-        <v>-21500</v>
+        <v>-128900</v>
       </c>
       <c r="F26" s="3">
+        <v>-22300</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="H26" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="I26" s="3">
+        <v>-190900</v>
+      </c>
+      <c r="J26" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="K26" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="L26" s="3">
+        <v>-2100</v>
+      </c>
+      <c r="M26" s="3">
+        <v>5400</v>
+      </c>
+      <c r="N26" s="3">
+        <v>-200</v>
+      </c>
+      <c r="O26" s="3">
+        <v>5300</v>
+      </c>
+      <c r="P26" s="3">
         <v>-2700</v>
       </c>
-      <c r="G26" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="H26" s="3">
-        <v>-191900</v>
-      </c>
-      <c r="I26" s="3">
-        <v>-6000</v>
-      </c>
-      <c r="J26" s="3">
-        <v>-5000</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="Q26" s="3">
+        <v>13500</v>
+      </c>
+      <c r="R26" s="3">
+        <v>15600</v>
+      </c>
+      <c r="S26" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="T26" s="3">
+        <v>38900</v>
+      </c>
+      <c r="U26" s="3">
+        <v>53600</v>
+      </c>
+      <c r="V26" s="3">
+        <v>16300</v>
+      </c>
+      <c r="W26" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="X26" s="3">
+        <v>8600</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-2100</v>
       </c>
-      <c r="L26" s="3">
-        <v>5400</v>
-      </c>
-      <c r="M26" s="3">
-        <v>-200</v>
-      </c>
-      <c r="N26" s="3">
-        <v>5300</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="P26" s="3">
-        <v>13500</v>
-      </c>
-      <c r="Q26" s="3">
-        <v>15600</v>
-      </c>
-      <c r="R26" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="S26" s="3">
-        <v>38900</v>
-      </c>
-      <c r="T26" s="3">
-        <v>53600</v>
-      </c>
-      <c r="U26" s="3">
-        <v>16300</v>
-      </c>
-      <c r="V26" s="3">
-        <v>-11400</v>
-      </c>
-      <c r="W26" s="3">
-        <v>8600</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-2100</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-128900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-22300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-5300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-4300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-190900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-6900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-28500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-31500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>13700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-1900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>35500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>14900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-12000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>6500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2118,31 +2176,34 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -2153,8 +2214,8 @@
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>-100</v>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3">
         <v>-100</v>
@@ -2163,34 +2224,37 @@
         <v>-100</v>
       </c>
       <c r="Q29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-200</v>
       </c>
-      <c r="S29" s="3">
+      <c r="T29" s="3">
         <v>-100</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-500</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-200</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>5400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-400</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>1000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2260,8 +2324,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2331,150 +2398,159 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>20000</v>
+        <v>-2600</v>
       </c>
       <c r="E32" s="3">
-        <v>18700</v>
+        <v>-500</v>
       </c>
       <c r="F32" s="3">
-        <v>18300</v>
+        <v>-800</v>
       </c>
       <c r="G32" s="3">
-        <v>17800</v>
+        <v>-2500</v>
       </c>
       <c r="H32" s="3">
-        <v>17000</v>
+        <v>-200</v>
       </c>
       <c r="I32" s="3">
-        <v>16000</v>
+        <v>1000</v>
       </c>
       <c r="J32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="K32" s="3">
         <v>15500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>15600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>15500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>15400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>14700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>17700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>8200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>18800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-10000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>23500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-128900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-22300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-5300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-4300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-190900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-6900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-28500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-31600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>13600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>35300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>14700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>6100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2544,155 +2620,164 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-128900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-22300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-5300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-4300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-190900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-6900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-28500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-31600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>13600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>35300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>14700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>6100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2718,8 +2803,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2745,79 +2831,83 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>48300</v>
+      </c>
+      <c r="E41" s="3">
         <v>10500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>12800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>14500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>72700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>88000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>194100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>133100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>126500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>290900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>299600</v>
-      </c>
-      <c r="R41" s="3">
-        <v>183300</v>
       </c>
       <c r="S41" s="3">
         <v>183300</v>
       </c>
       <c r="T41" s="3">
+        <v>183300</v>
+      </c>
+      <c r="U41" s="3">
         <v>41800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>254400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>61400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>40600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>29800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2887,79 +2977,85 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>375900</v>
+      </c>
+      <c r="E43" s="3">
         <v>403600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>362900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>375100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>340800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>346100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>299000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>296800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>272300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>279100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>280900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>237900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>302200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>239700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>223600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>210600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>172300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>177400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>175700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>183800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>201700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>161000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2972,35 +3068,35 @@
       <c r="F44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G44" s="3">
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3">
         <v>2300</v>
-      </c>
-      <c r="H44" s="3">
-        <v>1400</v>
       </c>
       <c r="I44" s="3">
         <v>1400</v>
       </c>
       <c r="J44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="K44" s="3">
         <v>2000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1700</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>8</v>
@@ -3017,8 +3113,8 @@
       <c r="U44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
@@ -3029,363 +3125,381 @@
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>14900</v>
+      </c>
+      <c r="F45" s="3">
+        <v>8800</v>
+      </c>
+      <c r="G45" s="3">
+        <v>7900</v>
+      </c>
+      <c r="H45" s="3">
+        <v>12000</v>
+      </c>
+      <c r="I45" s="3">
+        <v>9900</v>
+      </c>
+      <c r="J45" s="3">
+        <v>13400</v>
+      </c>
+      <c r="K45" s="3">
+        <v>32800</v>
+      </c>
+      <c r="L45" s="3">
+        <v>34800</v>
+      </c>
+      <c r="M45" s="3">
+        <v>26800</v>
+      </c>
+      <c r="N45" s="3">
+        <v>33200</v>
+      </c>
+      <c r="O45" s="3">
+        <v>37400</v>
+      </c>
+      <c r="P45" s="3">
+        <v>40200</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>26400</v>
+      </c>
+      <c r="R45" s="3">
+        <v>14100</v>
+      </c>
+      <c r="S45" s="3">
+        <v>32700</v>
+      </c>
+      <c r="T45" s="3">
+        <v>23800</v>
+      </c>
+      <c r="U45" s="3">
+        <v>26700</v>
+      </c>
+      <c r="V45" s="3">
+        <v>32700</v>
+      </c>
+      <c r="W45" s="3">
+        <v>11300</v>
+      </c>
+      <c r="X45" s="3">
+        <v>12600</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>45800</v>
+      </c>
+      <c r="Z45" s="3">
         <v>42500</v>
       </c>
-      <c r="E45" s="3">
-        <v>30800</v>
-      </c>
-      <c r="F45" s="3">
-        <v>27600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>36900</v>
-      </c>
-      <c r="H45" s="3">
-        <v>38500</v>
-      </c>
-      <c r="I45" s="3">
-        <v>35000</v>
-      </c>
-      <c r="J45" s="3">
-        <v>32800</v>
-      </c>
-      <c r="K45" s="3">
-        <v>34800</v>
-      </c>
-      <c r="L45" s="3">
-        <v>26800</v>
-      </c>
-      <c r="M45" s="3">
-        <v>33200</v>
-      </c>
-      <c r="N45" s="3">
-        <v>37400</v>
-      </c>
-      <c r="O45" s="3">
-        <v>40200</v>
-      </c>
-      <c r="P45" s="3">
-        <v>26400</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>14100</v>
-      </c>
-      <c r="R45" s="3">
-        <v>32700</v>
-      </c>
-      <c r="S45" s="3">
-        <v>23800</v>
-      </c>
-      <c r="T45" s="3">
-        <v>26700</v>
-      </c>
-      <c r="U45" s="3">
-        <v>32700</v>
-      </c>
-      <c r="V45" s="3">
-        <v>11300</v>
-      </c>
-      <c r="W45" s="3">
-        <v>12600</v>
-      </c>
-      <c r="X45" s="3">
-        <v>45800</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>42500</v>
-      </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>463400</v>
+      </c>
+      <c r="E46" s="3">
         <v>456700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>404000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>404900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>387900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>392900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>348200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>346200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>381700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>395800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>509100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>409800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>470700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>557000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>537200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>426600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>379300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>245900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>462800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>256400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>254900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>236600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>240000</v>
       </c>
     </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>45900</v>
+        <v>35800</v>
       </c>
       <c r="E47" s="3">
-        <v>59800</v>
+        <v>39300</v>
       </c>
       <c r="F47" s="3">
+        <v>40200</v>
+      </c>
+      <c r="G47" s="3">
         <v>41500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>45200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>45100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>43700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>41300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>43500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>80400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>83300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>83100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>134400</v>
-      </c>
-      <c r="P47" s="3">
-        <v>141200</v>
       </c>
       <c r="Q47" s="3">
         <v>141200</v>
       </c>
       <c r="R47" s="3">
+        <v>141200</v>
+      </c>
+      <c r="S47" s="3">
         <v>137500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>141300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>132000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>128100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>130900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>154500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>157900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>159500</v>
       </c>
     </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>124300</v>
+      </c>
+      <c r="E48" s="3">
         <v>123600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>126800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>125400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>121200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>118200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>116600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>108500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>105800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>103100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>99900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>97300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>96600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>76100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>59600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>58500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>39900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>40700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>41300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>43300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>42200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>40900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>981900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1001600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1126600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1146500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1166100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1185800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1388600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1408100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1428200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1449000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1395500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1415000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1422000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>775800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>781100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>790600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>222600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>227500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>153600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>155100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>156700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>158200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>159800</v>
       </c>
     </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3455,8 +3569,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3526,79 +3643,85 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>46300</v>
+      </c>
+      <c r="E52" s="3">
         <v>48400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>46800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>48900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>42600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>42900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>44500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>40200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>30700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>31400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>22200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>11600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>26200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>11400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>12200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3668,79 +3791,85 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1651700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1676100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1764000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1767300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1763100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1785000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1941500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1944300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1989800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2059600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2113000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2027400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2135200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1576200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1531800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1425900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>791600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>654300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>797100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>597400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>620500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>605800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>613400</v>
       </c>
     </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3766,8 +3895,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3793,102 +3923,106 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E57" s="3">
         <v>62000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>54600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>55200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>41800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>56000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>55000</v>
       </c>
       <c r="J57" s="3">
         <v>55000</v>
       </c>
       <c r="K57" s="3">
+        <v>55000</v>
+      </c>
+      <c r="L57" s="3">
         <v>44200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>10600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>38100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>33500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>16300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>33800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>8500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>26700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>38500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>183000</v>
+        <v>241800</v>
       </c>
       <c r="E58" s="3">
-        <v>121000</v>
+        <v>191500</v>
       </c>
       <c r="F58" s="3">
-        <v>113800</v>
+        <v>129600</v>
       </c>
       <c r="G58" s="3">
-        <v>83000</v>
+        <v>122500</v>
       </c>
       <c r="H58" s="3">
-        <v>126500</v>
+        <v>91900</v>
       </c>
       <c r="I58" s="3">
-        <v>15000</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>8</v>
+        <v>135800</v>
+      </c>
+      <c r="J58" s="3">
+        <v>24900</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>8</v>
@@ -3905,26 +4039,26 @@
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3" t="s">
+      <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>162300</v>
-      </c>
-      <c r="V58" s="3">
-        <v>300</v>
       </c>
       <c r="W58" s="3">
         <v>300</v>
@@ -3933,203 +4067,212 @@
         <v>300</v>
       </c>
       <c r="Y58" s="3">
+        <v>300</v>
+      </c>
+      <c r="Z58" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>323600</v>
+        <v>68600</v>
       </c>
       <c r="E59" s="3">
-        <v>363700</v>
+        <v>104200</v>
       </c>
       <c r="F59" s="3">
-        <v>351400</v>
+        <v>149100</v>
       </c>
       <c r="G59" s="3">
-        <v>392000</v>
+        <v>137200</v>
       </c>
       <c r="H59" s="3">
-        <v>350700</v>
+        <v>159900</v>
       </c>
       <c r="I59" s="3">
-        <v>424200</v>
+        <v>138400</v>
       </c>
       <c r="J59" s="3">
+        <v>203500</v>
+      </c>
+      <c r="K59" s="3">
         <v>436600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>489300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>542800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>574900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>518500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>542500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>513000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>452300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>316200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>243800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>192800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>128400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>140100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>157900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>150700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>165500</v>
       </c>
     </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>581500</v>
+      </c>
+      <c r="E60" s="3">
         <v>568600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>539300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>520400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>516900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>533200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>494200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>491600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>533500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>553400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>612900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>527200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>576000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>529200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>486100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>324800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>270600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>201300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>329100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>150200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>165800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>160600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>171500</v>
       </c>
     </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>986100</v>
+        <v>1020500</v>
       </c>
       <c r="E61" s="3">
-        <v>984900</v>
+        <v>1019200</v>
       </c>
       <c r="F61" s="3">
-        <v>983800</v>
+        <v>1019800</v>
       </c>
       <c r="G61" s="3">
-        <v>982600</v>
+        <v>1017500</v>
       </c>
       <c r="H61" s="3">
-        <v>981500</v>
+        <v>1016000</v>
       </c>
       <c r="I61" s="3">
-        <v>980400</v>
+        <v>1013900</v>
       </c>
       <c r="J61" s="3">
+        <v>1013300</v>
+      </c>
+      <c r="K61" s="3">
         <v>979400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>978300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>977300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>976200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>975200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>974700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>487400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>486700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>486000</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4140,87 +4283,93 @@
         <v>0</v>
       </c>
       <c r="W61" s="3">
+        <v>0</v>
+      </c>
+      <c r="X61" s="3">
         <v>100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>112000</v>
+        <v>33900</v>
       </c>
       <c r="E62" s="3">
-        <v>104000</v>
+        <v>33700</v>
       </c>
       <c r="F62" s="3">
-        <v>106900</v>
+        <v>33300</v>
       </c>
       <c r="G62" s="3">
-        <v>104700</v>
+        <v>33600</v>
       </c>
       <c r="H62" s="3">
-        <v>108800</v>
+        <v>29300</v>
       </c>
       <c r="I62" s="3">
-        <v>115800</v>
+        <v>29500</v>
       </c>
       <c r="J62" s="3">
+        <v>29400</v>
+      </c>
+      <c r="K62" s="3">
         <v>118800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>123900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>146900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>147600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>151700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>180500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>150300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>140200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>203600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>111000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>87300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>62500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>52400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>57700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>50500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4290,8 +4439,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4361,8 +4513,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4432,79 +4587,85 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1668700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1666600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1628200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1611100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1604200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1623600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1590400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1589700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1635700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1677600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1736800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1654200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1731200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1166900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1113000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1014300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>381600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>288600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>391600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>202700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>223700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>211400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>221100</v>
       </c>
     </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4530,8 +4691,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4601,8 +4763,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4672,8 +4837,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4726,25 +4894,28 @@
         <v>0</v>
       </c>
       <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
         <v>5300</v>
-      </c>
-      <c r="U70" s="3">
-        <v>77100</v>
       </c>
       <c r="V70" s="3">
         <v>77100</v>
       </c>
       <c r="W70" s="3">
-        <v>77200</v>
+        <v>77100</v>
       </c>
       <c r="X70" s="3">
         <v>77200</v>
       </c>
       <c r="Y70" s="3">
+        <v>77200</v>
+      </c>
+      <c r="Z70" s="3">
         <v>77400</v>
       </c>
     </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4814,79 +4985,85 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-202200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-175600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-46700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-24400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-19200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-14900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>176100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>180000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>187000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>215500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>212100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>211800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>243400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>250900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>237300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>218400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>221500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>185900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>198700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>183700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>190900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>183800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>186600</v>
       </c>
     </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4956,8 +5133,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5027,8 +5207,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5098,79 +5281,85 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-17000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>135800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>156200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>158900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>161400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>351100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>354600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>354100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>381900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>376200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>373300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>404000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>409300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>418800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>411600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>410100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>360500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>328400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>317600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>319700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>317200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5240,155 +5429,164 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-128900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-22300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-5300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-4300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-190900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-6900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-28500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-31600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>13600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>35300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>14700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>6100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5414,79 +5612,83 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>27800</v>
+        <v>6300</v>
       </c>
       <c r="E83" s="3">
-        <v>27100</v>
+        <v>6100</v>
       </c>
       <c r="F83" s="3">
-        <v>26600</v>
+        <v>5800</v>
       </c>
       <c r="G83" s="3">
-        <v>26100</v>
+        <v>17300</v>
       </c>
       <c r="H83" s="3">
-        <v>25900</v>
+        <v>4900</v>
       </c>
       <c r="I83" s="3">
+        <v>5000</v>
+      </c>
+      <c r="J83" s="3">
+        <v>4500</v>
+      </c>
+      <c r="K83" s="3">
+        <v>26000</v>
+      </c>
+      <c r="L83" s="3">
         <v>25700</v>
       </c>
-      <c r="J83" s="3">
-        <v>26000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>25700</v>
-      </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>24800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>23900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>20300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>11800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>9000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>7300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>9900</v>
-      </c>
-      <c r="U83" s="3">
-        <v>3800</v>
       </c>
       <c r="V83" s="3">
         <v>3800</v>
       </c>
       <c r="W83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="X83" s="3">
         <v>4100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5556,8 +5758,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5627,8 +5832,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5698,8 +5906,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5769,8 +5980,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5840,79 +6054,85 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-55300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-25600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>53500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-108200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-2700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-56000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-20300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>71500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>12100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>34500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>134600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>61200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>140000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>147200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>38800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>20900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>17000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>23100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5938,79 +6158,83 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-8900</v>
       </c>
       <c r="H91" s="3">
         <v>-8900</v>
       </c>
       <c r="I91" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="J91" s="3">
         <v>-13300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-1600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6080,8 +6304,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6151,79 +6378,85 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11100</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-8900</v>
       </c>
       <c r="H94" s="3">
         <v>-8900</v>
       </c>
       <c r="I94" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="J94" s="3">
         <v>-13300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-86200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-657100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-18600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-552600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-80000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-3600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6249,31 +6482,32 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6320,8 +6554,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6391,8 +6628,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6462,8 +6702,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6533,102 +6776,108 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E100" s="3">
         <v>62200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>31000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-43500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>111300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>14400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>5600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>487300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-24600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-12900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>487900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>4100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-83800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>155500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-6700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>3300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -6675,75 +6924,81 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E102" s="3">
         <v>200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>8100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-57800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-15300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-106500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>61100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-164200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-8700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>116300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>141700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-16600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>192800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>20000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>7300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>22100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>38300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MODV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MODV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>MODV</t>
   </si>
@@ -656,340 +656,352 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>702800</v>
+      </c>
+      <c r="E8" s="3">
         <v>702000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>698300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>684500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>702800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>686900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>699100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>662300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>653900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>647800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>628200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>574500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>575800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>493100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>474400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>453600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>398500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>320600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>649500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>367300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>384800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>393400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>731700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>367800</v>
       </c>
     </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>597600</v>
+      </c>
+      <c r="E9" s="3">
         <v>597900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>588100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>583600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>585500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>579200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>589300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>550300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>534000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>534600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>504200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>459300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>890300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>798500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>759100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>720700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>314500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>235500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>528800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>332700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>358400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>356300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>686400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>340500</v>
       </c>
     </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>105200</v>
+      </c>
+      <c r="E10" s="3">
         <v>104100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>110200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>100900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>117300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>107700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>109900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>112000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>119900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>113200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>124000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>115200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-314500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-305400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-284700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-267100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>84000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>85100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>120700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>34600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>26400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>37100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>45300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1016,8 +1028,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1090,8 +1103,11 @@
       <c r="Z12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1164,61 +1180,64 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>11800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>105300</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>180500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-2800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-3300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-1900</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>-2600</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1226,8 +1245,8 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1238,82 +1257,88 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E15" s="3">
         <v>27900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>27800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>27100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>26600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>26100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>25900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>25700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>26000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>25700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>24800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>23900</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>20300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>12600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>11800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>12200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>9000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>7300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>9900</v>
-      </c>
-      <c r="V15" s="3">
-        <v>3800</v>
       </c>
       <c r="W15" s="3">
         <v>3800</v>
       </c>
       <c r="X15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Y15" s="3">
         <v>4100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>8800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1337,156 +1362,163 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>698500</v>
+      </c>
+      <c r="E17" s="3">
         <v>696800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>691900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>687800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>687500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>675400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>694400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>655700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>647300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>635300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>605100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>559600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>555600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>480100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>447000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>424800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>377600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>277300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>590700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>357200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>377300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>376400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>731500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>364400</v>
       </c>
     </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E18" s="3">
         <v>5300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-3400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>11500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4700</v>
-      </c>
-      <c r="J18" s="3">
-        <v>6600</v>
       </c>
       <c r="K18" s="3">
         <v>6600</v>
       </c>
       <c r="L18" s="3">
+        <v>6600</v>
+      </c>
+      <c r="M18" s="3">
         <v>12500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>23100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>20200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>13000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>27400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>28800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>20900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>43300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>58800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>10100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>17000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1513,183 +1545,190 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E20" s="3">
         <v>2600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-15500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-15600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-15500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-15400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-14700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-17700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-8200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-18800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>10000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-23500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E21" s="3">
         <v>30600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>33700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>22900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>39300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>37400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>31600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>34400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>17100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>22600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>32400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>23400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>25800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>7900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>31000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>32600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>60600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>68900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>11000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-12100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>17800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E22" s="3">
         <v>28500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>20000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>18700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>16000</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
       <c r="L22" s="3">
         <v>0</v>
       </c>
@@ -1735,156 +1774,165 @@
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-37700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-119300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-22800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-6000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-191800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-5800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>7700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>5500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>19200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>20300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>53300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>59000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>7300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-16000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>13700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-3500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-11100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-500</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>-1700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>14400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-9000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-4500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1957,156 +2005,165 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-26600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-128900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-22300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-4300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-190900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-4000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-5000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-2100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>5400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>13500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>15600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>38900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>53600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>16300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-11400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>8600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-26600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-128900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-22300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-4300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-190900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-4000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-6900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-28500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>3300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-31500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>13700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>18800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>35500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>14900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-12000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>6500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-3800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2179,8 +2236,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2205,8 +2265,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -2217,8 +2277,8 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>-100</v>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P29" s="3">
         <v>-100</v>
@@ -2227,34 +2287,37 @@
         <v>-100</v>
       </c>
       <c r="R29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
         <v>-200</v>
       </c>
-      <c r="T29" s="3">
+      <c r="U29" s="3">
         <v>-100</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-500</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-200</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>5400</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>-400</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>1000</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2327,8 +2390,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2401,156 +2467,165 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-2600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>15500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>15600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>15500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>15400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>14700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>17700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>8200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>18800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-10000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>23500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-26600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-128900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-22300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-190900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-4000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-6900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-28500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>3300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-31600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>13600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>18800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>35300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>14700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-6700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>6100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2623,161 +2698,170 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-26600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-128900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-22300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-190900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-4000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-6900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-28500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>3300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-31600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>13600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>18800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>35300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>14700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-6700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>6100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2804,8 +2888,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2832,82 +2917,86 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>112600</v>
+      </c>
+      <c r="E41" s="3">
         <v>48300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>12800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>14500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>72700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>88000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>194100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>133100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>126500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>290900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>299600</v>
-      </c>
-      <c r="S41" s="3">
-        <v>183300</v>
       </c>
       <c r="T41" s="3">
         <v>183300</v>
       </c>
       <c r="U41" s="3">
+        <v>183300</v>
+      </c>
+      <c r="V41" s="3">
         <v>41800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>254400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>61400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>40600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>29800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2980,82 +3069,88 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>356800</v>
+      </c>
+      <c r="E43" s="3">
         <v>375900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>403600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>362900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>375100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>340800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>346100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>299000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>296800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>272300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>279100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>280900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>237900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>302200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>239700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>223600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>210600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>172300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>177400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>175700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>183800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>201700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>161000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3071,35 +3166,35 @@
       <c r="G44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3">
         <v>2300</v>
-      </c>
-      <c r="I44" s="3">
-        <v>1400</v>
       </c>
       <c r="J44" s="3">
         <v>1400</v>
       </c>
       <c r="K44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="L44" s="3">
         <v>2000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1700</v>
-      </c>
-      <c r="Q44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R44" s="3" t="s">
         <v>8</v>
@@ -3116,8 +3211,8 @@
       <c r="V44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="W44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
@@ -3128,378 +3223,396 @@
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E45" s="3">
         <v>15900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>14900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8800</v>
       </c>
-      <c r="G45" s="3">
-        <v>7900</v>
-      </c>
       <c r="H45" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I45" s="3">
         <v>12000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>32800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>34800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>33200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>37400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>40200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>26400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>14100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>32700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>23800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>26700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>32700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>11300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>12600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>45800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>495400</v>
+      </c>
+      <c r="E46" s="3">
         <v>463400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>456700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>404000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>404900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>387900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>392900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>348200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>346200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>381700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>395800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>509100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>409800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>470700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>557000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>537200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>426600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>379300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>245900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>462800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>256400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>254900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>236600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>240000</v>
       </c>
     </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>31400</v>
+      </c>
+      <c r="E47" s="3">
         <v>35800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>39300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>40200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>41500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>45200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>45100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>43700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>41300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>43500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>80400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>83300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>83100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>134400</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>141200</v>
       </c>
       <c r="R47" s="3">
         <v>141200</v>
       </c>
       <c r="S47" s="3">
+        <v>141200</v>
+      </c>
+      <c r="T47" s="3">
         <v>137500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>141300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>132000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>128100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>130900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>154500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>157900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>159500</v>
       </c>
     </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>119000</v>
+      </c>
+      <c r="E48" s="3">
         <v>124300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>123600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>126800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>125400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>121200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>118200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>116600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>108500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>105800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>103100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>99900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>97300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>96600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>76100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>59600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>58500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>39900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>40700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>41300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>43300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>42200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>40900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>962600</v>
+      </c>
+      <c r="E49" s="3">
         <v>981900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1001600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1126600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1146500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1166100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1185800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1388600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1408100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1428200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1449000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1395500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1415000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1422000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>775800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>781100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>790600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>222600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>227500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>153600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>155100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>156700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>158200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>159800</v>
       </c>
     </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3572,8 +3685,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3646,82 +3762,88 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>45900</v>
+      </c>
+      <c r="E52" s="3">
         <v>46300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>48400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>46800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>48900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>42600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>42900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>44500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>40200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>30700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>31400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>22200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>11600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>26200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>12700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>8600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>11400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>12200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3794,82 +3916,88 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1654300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1651700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1676100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1764000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1767300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1763100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1785000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1941500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1944300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1989800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2059600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2113000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2027400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2135200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1576200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1531800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1425900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>791600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>654300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>797100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>597400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>620500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>605800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>613400</v>
       </c>
     </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3896,8 +4024,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3924,108 +4053,112 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>83100</v>
+      </c>
+      <c r="E57" s="3">
         <v>52100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>62000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>54600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>55200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>41800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>56000</v>
-      </c>
-      <c r="J57" s="3">
-        <v>55000</v>
       </c>
       <c r="K57" s="3">
         <v>55000</v>
       </c>
       <c r="L57" s="3">
+        <v>55000</v>
+      </c>
+      <c r="M57" s="3">
         <v>44200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>10600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>38100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>8700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>33500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>33800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>8500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>26700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>8300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>38500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>7600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>9600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>282900</v>
+      </c>
+      <c r="E58" s="3">
         <v>241800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>191500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>129600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>122500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>91900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>135800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>24900</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>8</v>
@@ -4042,26 +4175,26 @@
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3" t="s">
+      <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>162300</v>
-      </c>
-      <c r="W58" s="3">
-        <v>300</v>
       </c>
       <c r="X58" s="3">
         <v>300</v>
@@ -4070,212 +4203,221 @@
         <v>300</v>
       </c>
       <c r="Z58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AA58" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>45000</v>
+      </c>
+      <c r="E59" s="3">
         <v>68600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>104200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>149100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>137200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>159900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>138400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>203500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>436600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>489300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>542800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>574900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>518500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>542500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>513000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>452300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>316200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>243800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>192800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>128400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>140100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>157900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>150700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>165500</v>
       </c>
     </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>624500</v>
+      </c>
+      <c r="E60" s="3">
         <v>581500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>568600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>539300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>520400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>516900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>533200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>494200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>491600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>533500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>553400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>612900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>527200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>576000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>529200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>486100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>324800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>270600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>201300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>329100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>150200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>165800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>160600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>171500</v>
       </c>
     </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1019300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1020500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1019200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1019800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1017500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1016000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1013900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1013300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>979400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>978300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>977300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>976200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>975200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>974700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>487400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>486700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>486000</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4286,90 +4428,96 @@
         <v>0</v>
       </c>
       <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
         <v>100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E62" s="3">
         <v>33900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>33700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>33300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>33600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>29300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>29500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>29400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>118800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>123900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>146900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>147600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>151700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>180500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>150300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>140200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>203600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>111000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>87300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>62500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>52400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>57700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>50500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4442,8 +4590,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4516,8 +4667,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4590,82 +4744,88 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1692800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1668700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1666600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1628200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1611100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1604200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1623600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1590400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1589700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1635700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1677600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1736800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1654200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1731200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1166900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1113000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1014300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>381600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>288600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>391600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>202700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>223700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>211400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>221100</v>
       </c>
     </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4692,8 +4852,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4766,8 +4927,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4840,8 +5004,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4897,25 +5064,28 @@
         <v>0</v>
       </c>
       <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
         <v>5300</v>
-      </c>
-      <c r="V70" s="3">
-        <v>77100</v>
       </c>
       <c r="W70" s="3">
         <v>77100</v>
       </c>
       <c r="X70" s="3">
-        <v>77200</v>
+        <v>77100</v>
       </c>
       <c r="Y70" s="3">
         <v>77200</v>
       </c>
       <c r="Z70" s="3">
+        <v>77200</v>
+      </c>
+      <c r="AA70" s="3">
         <v>77400</v>
       </c>
     </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4988,82 +5158,88 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-225700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-202200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-175600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-46700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-24400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-19200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-14900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>176100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>180000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>187000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>215500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>212100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>211800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>243400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>250900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>237300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>218400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>221500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>185900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>198700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>183700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>190900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>183800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>186600</v>
       </c>
     </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5136,8 +5312,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5210,8 +5389,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5284,82 +5466,88 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-17000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>135800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>156200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>158900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>161400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>351100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>354600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>354100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>381900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>376200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>373300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>404000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>409300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>418800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>411600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>410100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>360500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>328400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>317600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>319700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>317200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5432,161 +5620,170 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-26600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-128900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-22300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-190900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-4000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-6900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-28500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>3300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-31600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>13600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>18800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>35300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>14700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-6700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>6100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5613,82 +5810,86 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E83" s="3">
         <v>6300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>17300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>26000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>25700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>24800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>23900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>20300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>12600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>11800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>12200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>9000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>7300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>9900</v>
-      </c>
-      <c r="V83" s="3">
-        <v>3800</v>
       </c>
       <c r="W83" s="3">
         <v>3800</v>
       </c>
       <c r="X83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Y83" s="3">
         <v>4100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5761,8 +5962,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5835,8 +6039,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5909,8 +6116,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5983,8 +6193,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6057,82 +6270,88 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E89" s="3">
         <v>9300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-55300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>9600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-25600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>53500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-108200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-2700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-56000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-20300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>71500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>12100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>34500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>134600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>61200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>140000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>147200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>38800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>20900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>17000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>23100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6159,82 +6378,86 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-7700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-8900</v>
       </c>
       <c r="I91" s="3">
         <v>-8900</v>
       </c>
       <c r="J91" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="K91" s="3">
         <v>-13300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6307,8 +6530,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6381,82 +6607,88 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11100</v>
-      </c>
-      <c r="H94" s="3">
-        <v>-8900</v>
       </c>
       <c r="I94" s="3">
         <v>-8900</v>
       </c>
       <c r="J94" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="K94" s="3">
         <v>-13300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-86200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-657100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-552600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-2500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-80000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-3600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6483,8 +6715,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6509,8 +6742,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6557,8 +6790,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6631,8 +6867,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6705,8 +6944,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6779,82 +7021,88 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>39500</v>
+      </c>
+      <c r="E100" s="3">
         <v>36300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>62200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>31000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-43500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>111300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>14400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>5600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>487300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-24600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-12900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>487900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>4100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-83800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>155500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6879,8 +7127,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -6927,78 +7175,84 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>64200</v>
+      </c>
+      <c r="E102" s="3">
         <v>37800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-57800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-15300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-106500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>61100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-164200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-8700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>116300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>141700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-16600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>192800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>20000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>7300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>22100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>38300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MODV_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MODV_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>MODV</t>
   </si>
@@ -656,352 +656,365 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>650700</v>
+      </c>
+      <c r="E8" s="3">
         <v>702800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>702000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>698300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>684500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>702800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>686900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>699100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>662300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>653900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>647800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>628200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>574500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>575800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>493100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>474400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>453600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>398500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>320600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>649500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>367300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>384800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>393400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>731700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>367800</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>553000</v>
+      </c>
+      <c r="E9" s="3">
         <v>597600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>597900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>588100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>583600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>585500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>579200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>589300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>550300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>534000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>534600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>504200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>459300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>890300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>798500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>759100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>720700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>314500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>235500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>528800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>332700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>358400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>356300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>686400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>340500</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E10" s="3">
         <v>105200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>104100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>110200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>100900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>117300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>107700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>109900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>112000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>119900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>113200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>124000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>115200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-314500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-305400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-284700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-267100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>84000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>85100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>120700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>34600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>26400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>37100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>45300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>27300</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1029,8 +1042,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1106,8 +1120,11 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1183,64 +1200,67 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>11800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>105300</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>180500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-1500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-2800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-3300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-500</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-1900</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-2600</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1248,8 +1268,8 @@
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1260,85 +1280,91 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>23500</v>
+      </c>
+      <c r="E15" s="3">
         <v>26700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>27900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>27800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>27100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>26600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>26100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>25900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>25700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>26000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>25700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>24800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>23900</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>20300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>12600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>11800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>12200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>9000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>7300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>9900</v>
-      </c>
-      <c r="W15" s="3">
-        <v>3800</v>
       </c>
       <c r="X15" s="3">
         <v>3800</v>
       </c>
       <c r="Y15" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Z15" s="3">
         <v>4100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>8800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1363,162 +1389,169 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>655100</v>
+      </c>
+      <c r="E17" s="3">
         <v>698500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>696800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>691900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>687800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>687500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>675400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>694400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>655700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>647300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>635300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>605100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>559600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>555600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>480100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>447000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>424800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>377600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>277300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>590700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>357200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>377300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>376400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>731500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>364400</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="E18" s="3">
         <v>4300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-3400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>15300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4700</v>
-      </c>
-      <c r="K18" s="3">
-        <v>6600</v>
       </c>
       <c r="L18" s="3">
         <v>6600</v>
       </c>
       <c r="M18" s="3">
+        <v>6600</v>
+      </c>
+      <c r="N18" s="3">
         <v>12500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>23100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>20200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>13000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>27400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>28800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>20900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>43300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>58800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>17000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1546,192 +1579,199 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E20" s="3">
         <v>4300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-15500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-15600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-15500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-15400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-14700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-17700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-8200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-8400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-18800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>10000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-23500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1900</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E21" s="3">
         <v>26700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>30600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>33700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>22900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>39300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>37400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>31600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>34400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>17100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>22600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>32400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>23400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>25800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>7900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>31000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>32600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>11100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>60600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>68900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>11000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-12100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>17800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>5600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6000</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E22" s="3">
         <v>26900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>28500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>20000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>18400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>16000</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
       <c r="M22" s="3">
         <v>0</v>
       </c>
@@ -1777,162 +1817,171 @@
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-46800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-26900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-37700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-119300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-22800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-5200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-6000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-191800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-5800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-8900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>7700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>5500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-4700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>19200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>20300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>53300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>59000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>7300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-16000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>13700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>1500</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-3500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-11100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-500</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>-1700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-2000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>14400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-9000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-4500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2008,162 +2057,171 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-23500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-26600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-128900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-22300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-5300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-4300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-190900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-4000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-5000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-2100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>5300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>13500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>38900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>53600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>16300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-11400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>8600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>1300</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-23500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-26600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-128900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-22300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-5300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-4300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-190900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-4000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-6900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-28500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-31500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-7600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>13700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>18800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-1900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>35500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>14900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>6500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-3800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>200</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2239,8 +2297,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2268,8 +2329,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -2280,8 +2341,8 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>-100</v>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q29" s="3">
         <v>-100</v>
@@ -2290,34 +2351,37 @@
         <v>-100</v>
       </c>
       <c r="S29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
         <v>-200</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-100</v>
       </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
         <v>-500</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>-200</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>5400</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-400</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>1000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2393,8 +2457,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2470,162 +2537,171 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>15500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>15600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>15500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>15400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>14700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>17700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>8200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>8400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>18800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-10000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>23500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1900</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-23500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-26600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-128900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-22300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-5300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-190900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-4000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-6900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-28500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-31600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-7700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>13600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>18800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>35300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>14700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>6100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2701,167 +2777,176 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-23500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-26600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-128900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-22300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-5300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-190900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-4000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-6900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-28500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-31600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-7700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>13600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>18800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>35300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>14700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>6100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2889,8 +2974,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2918,85 +3004,89 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E41" s="3">
         <v>112600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>48300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>10300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>12800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>14500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>72700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>88000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>194100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>133100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>126500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>290900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>299600</v>
-      </c>
-      <c r="T41" s="3">
-        <v>183300</v>
       </c>
       <c r="U41" s="3">
         <v>183300</v>
       </c>
       <c r="V41" s="3">
+        <v>183300</v>
+      </c>
+      <c r="W41" s="3">
         <v>41800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>254400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>61400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>40600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>29800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>42400</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3072,85 +3162,91 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>381000</v>
+      </c>
+      <c r="E43" s="3">
         <v>356800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>375900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>403600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>362900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>375100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>340800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>346100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>299000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>296800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>272300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>279100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>280900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>237900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>302200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>239700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>223600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>210600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>172300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>177400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>175700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>183800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>201700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>161000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>155100</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3169,35 +3265,35 @@
       <c r="H44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I44" s="3">
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3">
         <v>2300</v>
-      </c>
-      <c r="J44" s="3">
-        <v>1400</v>
       </c>
       <c r="K44" s="3">
         <v>1400</v>
       </c>
       <c r="L44" s="3">
+        <v>1400</v>
+      </c>
+      <c r="M44" s="3">
         <v>2000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1700</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S44" s="3" t="s">
         <v>8</v>
@@ -3214,8 +3310,8 @@
       <c r="W44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
@@ -3226,393 +3322,411 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E45" s="3">
         <v>6400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>14900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>32800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>34800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>26800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>33200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>37400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>40200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>14100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>32700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>23800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>26700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>32700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>11300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>12600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>45800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>533400</v>
+      </c>
+      <c r="E46" s="3">
         <v>495400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>463400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>456700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>404000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>404900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>387900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>392900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>348200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>346200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>381700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>395800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>509100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>409800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>470700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>557000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>537200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>426600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>379300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>245900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>462800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>256400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>254900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>236600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>240000</v>
       </c>
     </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E47" s="3">
         <v>31400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>35800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>39300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>40200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>41500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>45200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>45100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>43700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>41300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>43500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>80400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>83300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>83100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>134400</v>
-      </c>
-      <c r="R47" s="3">
-        <v>141200</v>
       </c>
       <c r="S47" s="3">
         <v>141200</v>
       </c>
       <c r="T47" s="3">
+        <v>141200</v>
+      </c>
+      <c r="U47" s="3">
         <v>137500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>141300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>132000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>128100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>130900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>154500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>157900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>159500</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>112400</v>
+      </c>
+      <c r="E48" s="3">
         <v>119000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>124300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>123600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>126800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>125400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>121200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>118200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>116600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>108500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>105800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>103100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>99900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>97300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>96600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>76100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>59600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>58500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>39900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>40700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>41300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>43300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>42200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>40900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>42900</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>946500</v>
+      </c>
+      <c r="E49" s="3">
         <v>962600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>981900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1001600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1126600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1146500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1166100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1185800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1388600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1408100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1428200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1449000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1395500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1415000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1422000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>775800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>781100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>790600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>222600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>227500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>153600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>155100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>156700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>158200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>159800</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3688,8 +3802,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3765,8 +3882,11 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3774,76 +3894,79 @@
         <v>45900</v>
       </c>
       <c r="E52" s="3">
+        <v>45900</v>
+      </c>
+      <c r="F52" s="3">
         <v>46300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>48400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>46800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>48900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>42600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>42900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>44500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>40200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>31400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>22200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>11600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>26200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>12700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>12800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>11400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>11600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>12200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>12100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>11100</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3919,85 +4042,91 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1677200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1654300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1651700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1676100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1764000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1767300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1763100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1785000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1941500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1944300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1989800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2059600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2113000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2027400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2135200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1576200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1531800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1425900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>791600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>654300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>797100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>597400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>620500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>605800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>613400</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4025,8 +4154,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4054,114 +4184,118 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>57700</v>
+      </c>
+      <c r="E57" s="3">
         <v>83100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>52100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>62000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>54600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>55200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>41800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>56000</v>
-      </c>
-      <c r="K57" s="3">
-        <v>55000</v>
       </c>
       <c r="L57" s="3">
         <v>55000</v>
       </c>
       <c r="M57" s="3">
+        <v>55000</v>
+      </c>
+      <c r="N57" s="3">
         <v>44200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>38100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>33500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>33800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>8500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>26700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>38500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>9800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>7600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>9600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>352800</v>
+      </c>
+      <c r="E58" s="3">
         <v>282900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>241800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>191500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>129600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>122500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>91900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>135800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>24900</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>8</v>
@@ -4178,26 +4312,26 @@
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
-      <c r="S58" s="3" t="s">
+      <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>162300</v>
-      </c>
-      <c r="X58" s="3">
-        <v>300</v>
       </c>
       <c r="Y58" s="3">
         <v>300</v>
@@ -4206,221 +4340,230 @@
         <v>300</v>
       </c>
       <c r="AA58" s="3">
+        <v>300</v>
+      </c>
+      <c r="AB58" s="3">
         <v>700</v>
       </c>
     </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>51200</v>
+      </c>
+      <c r="E59" s="3">
         <v>45000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>68600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>104200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>149100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>137200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>159900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>138400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>203500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>436600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>489300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>542800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>574900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>518500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>542500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>513000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>452300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>316200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>243800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>192800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>128400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>140100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>157900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>150700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>165500</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>667700</v>
+      </c>
+      <c r="E60" s="3">
         <v>624500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>581500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>568600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>539300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>520400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>516900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>533200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>494200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>491600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>533500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>553400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>612900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>527200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>576000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>529200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>486100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>324800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>270600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>201300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>329100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>150200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>165800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>160600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>171500</v>
       </c>
     </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1047900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1019300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1020500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1019200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1019800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1017500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1016000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1013900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1013300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>979400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>978300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>977300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>976200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>975200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>974700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>487400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>486700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>486000</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4431,93 +4574,99 @@
         <v>0</v>
       </c>
       <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="3">
         <v>100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>300</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>35700</v>
+      </c>
+      <c r="E62" s="3">
         <v>35400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>33900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>33700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>33300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>33600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>29300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>29500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>29400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>118800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>123900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>146900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>147600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>151700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>180500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>150300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>140200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>203600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>111000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>87300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>62500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>52400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>57700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>50500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>49300</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4593,8 +4742,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4670,8 +4822,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4747,85 +4902,91 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1764800</v>
+      </c>
+      <c r="E66" s="3">
         <v>1692800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1668700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1666600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1628200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1611100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1604200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1623600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1590400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1589700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1635700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1677600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1736800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1654200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1731200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1166900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1113000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1014300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>381600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>288600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>391600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>202700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>223700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>211400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>221100</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4853,8 +5014,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4930,8 +5092,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5007,8 +5172,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5067,25 +5235,28 @@
         <v>0</v>
       </c>
       <c r="V70" s="3">
+        <v>0</v>
+      </c>
+      <c r="W70" s="3">
         <v>5300</v>
-      </c>
-      <c r="W70" s="3">
-        <v>77100</v>
       </c>
       <c r="X70" s="3">
         <v>77100</v>
       </c>
       <c r="Y70" s="3">
-        <v>77200</v>
+        <v>77100</v>
       </c>
       <c r="Z70" s="3">
         <v>77200</v>
       </c>
       <c r="AA70" s="3">
+        <v>77200</v>
+      </c>
+      <c r="AB70" s="3">
         <v>77400</v>
       </c>
     </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5161,85 +5332,91 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-276100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-225700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-202200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-175600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-46700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-24400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-19200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-14900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>176100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>180000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>187000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>215500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>212100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>211800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>243400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>250900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>237300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>218400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>221500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>185900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>198700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>183700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>190900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>183800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>186600</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5315,8 +5492,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5392,8 +5572,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5469,85 +5652,91 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-87600</v>
+      </c>
+      <c r="E76" s="3">
         <v>-38500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-17000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>135800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>156200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>158900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>161400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>351100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>354600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>354100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>381900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>376200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>373300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>404000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>409300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>418800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>411600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>410100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>360500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>328400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>317600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>319700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>317200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>314900</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5623,167 +5812,176 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-50400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-23500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-26600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-128900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-22300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-5300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-190900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-4000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-6900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-28500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-31600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-7700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>13600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>18800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>35300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>14700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>6100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-500</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5811,85 +6009,89 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E83" s="3">
         <v>16300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>17300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>5000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>26000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>25700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>23900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>20300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>12600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>11800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>12200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>9000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>7300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>9900</v>
-      </c>
-      <c r="W83" s="3">
-        <v>3800</v>
       </c>
       <c r="X83" s="3">
         <v>3800</v>
       </c>
       <c r="Y83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="Z83" s="3">
         <v>4100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>8800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>4500</v>
       </c>
     </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5965,8 +6167,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6042,8 +6247,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6119,8 +6327,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6196,8 +6407,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6273,85 +6487,91 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-82100</v>
+      </c>
+      <c r="E89" s="3">
         <v>30000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-55300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>9600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-25600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>53500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-108200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-2700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-56000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-5700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-20300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>71500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>12100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>5600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>34500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>134600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>61200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>140000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>147200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>38800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>20900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>17000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>23100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6379,85 +6599,89 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-5300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-8900</v>
       </c>
       <c r="J91" s="3">
         <v>-8900</v>
       </c>
       <c r="K91" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="L91" s="3">
         <v>-13300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-1600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6533,8 +6757,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6610,85 +6837,91 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11100</v>
-      </c>
-      <c r="I94" s="3">
-        <v>-8900</v>
       </c>
       <c r="J94" s="3">
         <v>-8900</v>
       </c>
       <c r="K94" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="L94" s="3">
         <v>-13300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-86200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-8600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-657100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-18600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-552600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-80000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1700</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6716,8 +6949,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6745,8 +6979,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -6793,8 +7027,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6870,8 +7107,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6947,8 +7187,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7024,85 +7267,91 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>93000</v>
+      </c>
+      <c r="E100" s="3">
         <v>39500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>36300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>62200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>31000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-43500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>111300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>14400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>5600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>487300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-24600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-12900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>487900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>4100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-83800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>155500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-6700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7130,8 +7379,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7178,81 +7427,87 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E102" s="3">
         <v>64200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>37800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-5900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-57800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-15300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-106500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>61100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-164200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-8700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>116300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>141700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-16600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>192800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>20000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>7300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>22100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>38300</v>
       </c>
     </row>
